--- a/EXCEL/Data/Køn_data/køn_stilling.xlsx
+++ b/EXCEL/Data/Køn_data/køn_stilling.xlsx
@@ -154,7 +154,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 13.57.55</t>
+    <t>Kørsel 14.4.2026 12.27.54</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
